--- a/artfynd/A 22084-2026 artfynd.xlsx
+++ b/artfynd/A 22084-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128462844</v>
+        <v>128627678</v>
       </c>
       <c r="B2" t="n">
-        <v>57720</v>
+        <v>92567</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6031</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -708,31 +708,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+          <t>Flatehult 3:17, Grönskåra, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547230</v>
+        <v>547162</v>
       </c>
       <c r="R2" t="n">
-        <v>6323341</v>
+        <v>6323432</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,7 +756,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -771,7 +766,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,6 +775,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -798,35 +794,44 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128462848</v>
+        <v>128606301</v>
       </c>
       <c r="B3" t="n">
-        <v>58400</v>
+        <v>56814</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>100015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
@@ -836,22 +841,22 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>autobox</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+          <t>Ledningsgatan, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>547230</v>
+        <v>547184</v>
       </c>
       <c r="R3" t="n">
-        <v>6323341</v>
+        <v>6323479</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,22 +880,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-43 med Pettersson u384</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,44 +927,44 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128462835</v>
+        <v>128462844</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1040,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128462828</v>
+        <v>128606318</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
+        <v>56827</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,53 +1061,58 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100087</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fransfladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Myotis nattereri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>registreringar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>autobox</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+          <t>Ledningsgatan, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>547093</v>
+        <v>547184</v>
       </c>
       <c r="R5" t="n">
-        <v>6323391</v>
+        <v>6323479</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1121,22 +1136,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-43 med Pettersson u384</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,64 +1183,69 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128462822</v>
+        <v>128606329</v>
       </c>
       <c r="B6" t="n">
-        <v>57883</v>
+        <v>56830</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100092</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>registreringar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>autobox</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+          <t>Ledningsgatan, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>547152</v>
+        <v>547184</v>
       </c>
       <c r="R6" t="n">
-        <v>6323292</v>
+        <v>6323479</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1244,22 +1269,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-43 med Pettersson u384</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1286,10 +1316,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128462856</v>
+        <v>128582313</v>
       </c>
       <c r="B7" t="n">
-        <v>58093</v>
+        <v>57132</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,16 +1327,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1314,12 +1344,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1333,10 +1367,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>547230</v>
+        <v>547209</v>
       </c>
       <c r="R7" t="n">
-        <v>6323341</v>
+        <v>6323428</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1363,22 +1397,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>stöttes</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1405,44 +1444,44 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128582282</v>
+        <v>128973262</v>
       </c>
       <c r="B8" t="n">
-        <v>57883</v>
+        <v>57132</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1456,13 +1495,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>547270</v>
+        <v>547334</v>
       </c>
       <c r="R8" t="n">
-        <v>6323302</v>
+        <v>6323271</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1486,22 +1525,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1528,27 +1567,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128582313</v>
+        <v>128462856</v>
       </c>
       <c r="B9" t="n">
-        <v>56904</v>
+        <v>58327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1556,16 +1595,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1579,10 +1614,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>547209</v>
+        <v>547230</v>
       </c>
       <c r="R9" t="n">
-        <v>6323428</v>
+        <v>6323341</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1609,27 +1644,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>stöttes</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1656,59 +1686,64 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128627678</v>
+        <v>128427387</v>
       </c>
       <c r="B10" t="n">
-        <v>92161</v>
+        <v>58114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6031</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Flatehult 3:17, Grönskåra, Sm</t>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>547162</v>
+        <v>547064</v>
       </c>
       <c r="R10" t="n">
-        <v>6323432</v>
+        <v>6323460</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1732,22 +1767,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1756,7 +1791,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1772,6 +1806,883 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128462822</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>547152</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6323292</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128462828</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>547093</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6323391</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128462835</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>547230</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6323341</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128582282</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>547270</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6323302</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128462848</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>547230</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6323341</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128606326</v>
+      </c>
+      <c r="B16" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ledningsgatan, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>547184</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6323479</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-43 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128606312</v>
+      </c>
+      <c r="B17" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ledningsgatan, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>547184</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6323479</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-43 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22084-2026 artfynd.xlsx
+++ b/artfynd/A 22084-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128627678</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -924,6 +934,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128606301</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1047,6 +1062,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128462844</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1180,6 +1200,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128606318</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1313,6 +1338,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128606329</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1441,6 +1471,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128582313</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1564,6 +1599,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128973262</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1683,6 +1723,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128462856</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1806,6 +1851,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128427387</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1929,6 +1979,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128462822</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2052,6 +2107,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128462828</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2175,6 +2235,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128462835</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2298,6 +2363,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128582282</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2417,6 +2487,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128462848</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2550,6 +2625,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128606326</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2683,8 +2763,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128606312</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>